--- a/resources/templates/standard/B1100-01.xlsx
+++ b/resources/templates/standard/B1100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>부적합품 발생 통보서</t>
   </si>
@@ -669,12 +672,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -693,20 +698,20 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4"/>
@@ -750,7 +755,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -781,7 +786,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -793,7 +798,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
       <c r="K4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -805,7 +810,7 @@
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -820,7 +825,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -832,7 +837,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
@@ -844,7 +849,7 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
@@ -859,7 +864,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -871,7 +876,7 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -883,7 +888,7 @@
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
       <c r="U6" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -932,7 +937,7 @@
     <row r="8" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -1000,7 +1005,7 @@
     <row r="10" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -1332,7 +1337,7 @@
     <row r="20" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -1598,7 +1603,7 @@
     <row r="28" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -1830,13 +1835,13 @@
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
       <c r="E35" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
@@ -1871,7 +1876,7 @@
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
       <c r="E36" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
@@ -1906,7 +1911,7 @@
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
       <c r="E37" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
